--- a/Supplemental_data/Supplemental data 15.xlsx
+++ b/Supplemental_data/Supplemental data 15.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="314">
   <si>
-    <t>Shared DEDMGs that were upregulated or downregulated in both ecotypes and exhibititng opposite methylation changes in same sequence context and genic region of both ecotypes</t>
+    <t>Shared differentially expressed differentially methylated genes with similar regulation between ecotypes, and opposite methylation patterns in regions and contexts.</t>
   </si>
   <si>
     <t>Expression data for each ecotype follows the same order as the ecotype positions in column A</t>
